--- a/docs/Report (4).xlsx
+++ b/docs/Report (4).xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nestech\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nestech\Downloads\Compressed\Matrix2-main\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C877743F-E208-4EEC-89D8-8F2D61AA6DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6D8E36-078F-470F-AA24-028303C3323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="1813">
   <si>
     <t>پیدا کردن ردیف پشتیبان از فیلد 141</t>
   </si>
@@ -5436,33 +5436,15 @@
     <t>کد رشته</t>
   </si>
   <si>
-    <t>جنسیت (0 یا 1)</t>
-  </si>
-  <si>
-    <t>دانش آموز - فارغ التحصیل (1 یا 0)</t>
-  </si>
-  <si>
     <t>خالی</t>
   </si>
   <si>
     <t>کد جایگزین پشتیبان</t>
   </si>
   <si>
-    <t>عادی حکمت بنیاد (0 یا 3 یا 1)</t>
-  </si>
-  <si>
-    <t>شماره پرونده بنیاد شهید (اگر وضعیت ثبت نام 1 باشد)</t>
-  </si>
-  <si>
     <t>کد مدرسه</t>
   </si>
   <si>
-    <t>کد رهگیری حکمت (اگر وضعیت ثبت نام 3 باشد مقدار این سلول میشه 1111111111111111)</t>
-  </si>
-  <si>
-    <t>تلفن منزل (اگر وضعیت ثبت نام 3 بود و این سلول خالی بود به جای آن 00000000000 گذاشته شود</t>
-  </si>
-  <si>
     <t>مقدار برای مپ کردن از اکسل ورودی</t>
   </si>
   <si>
@@ -5479,13 +5461,25 @@
   </si>
   <si>
     <t>بر اساس نامی که در برنامه برای این ستون انتخاب شده</t>
+  </si>
+  <si>
+    <t>student_landline</t>
+  </si>
+  <si>
+    <t>hekmat_tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانش آموز - فارغ التحصیل </t>
+  </si>
+  <si>
+    <t>عادی حکمت بنیاد</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5494,12 +5488,19 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="B Titr"/>
       <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5522,7 +5523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5530,6 +5531,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5654,12 +5656,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1D57180-FE09-4FFB-AB28-4D1A0E54B096}" name="Table1" displayName="Table1" ref="A1:E60" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1D57180-FE09-4FFB-AB28-4D1A0E54B096}" name="Table1" displayName="Table1" ref="A1:E60" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E60" xr:uid="{B1D57180-FE09-4FFB-AB28-4D1A0E54B096}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9D87C829-A0DC-4221-A124-38230F03D356}" name="عنوان ستون ها ورودی" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{2D577FB1-5E9C-44F8-A078-103C6D01D883}" name="مقدار برای مپ کردن از اکسل ورودی" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{91B85598-8584-4880-904A-2535822AA683}" name="اولویت و ترتیب در اکسل خروجی" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{9D87C829-A0DC-4221-A124-38230F03D356}" name="عنوان ستون ها ورودی" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{2D577FB1-5E9C-44F8-A078-103C6D01D883}" name="مقدار برای مپ کردن از اکسل ورودی" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{91B85598-8584-4880-904A-2535822AA683}" name="اولویت و ترتیب در اکسل خروجی" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{88B850DE-BA65-4D64-8B35-C011958544B5}" name="مقدار از کجا آورده شود" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{2C3E1151-74D4-45DF-A769-B8FB3412300A}" name="عنوان ستون در خروجی اکسل" dataDxfId="0"/>
   </tableColumns>
@@ -23553,24 +23555,24 @@
     <col min="5" max="5" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1794</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1809</v>
+        <v>1803</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1795</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1810</v>
+        <v>1804</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1813</v>
+        <v>1807</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -23581,13 +23583,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -23599,10 +23601,10 @@
         <v>1797</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -23614,10 +23616,10 @@
         <v>1797</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -23629,10 +23631,10 @@
         <v>1797</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -23643,13 +23645,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -23660,64 +23662,64 @@
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1800</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="C9" s="2">
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C10" s="2">
         <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -23728,13 +23730,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -23745,13 +23747,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -23762,13 +23764,13 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -23779,13 +23781,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -23796,64 +23798,64 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1801</v>
+        <v>1811</v>
       </c>
       <c r="C16" s="2">
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C17" s="2">
         <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1808</v>
+      <c r="B18" s="3" t="s">
+        <v>1809</v>
       </c>
       <c r="C18" s="2">
         <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -23864,268 +23866,268 @@
         <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C20" s="2">
         <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C21" s="2">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C22" s="2">
         <v>18</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C23" s="2">
         <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C24" s="2">
         <v>20</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C25" s="2">
         <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C26" s="2">
         <v>22</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C27" s="2">
         <v>23</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C28" s="2">
         <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C29" s="2">
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C30" s="2">
         <v>26</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C31" s="2">
         <v>27</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C32" s="2">
         <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1805</v>
+        <v>29</v>
       </c>
       <c r="C33" s="2">
         <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C34" s="2">
         <v>30</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
@@ -24136,30 +24138,30 @@
         <v>31</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C36" s="2">
         <v>32</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
@@ -24170,30 +24172,30 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C38" s="2">
         <v>34</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
@@ -24204,13 +24206,13 @@
         <v>35</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
@@ -24221,30 +24223,30 @@
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C41" s="2">
         <v>37</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
@@ -24255,13 +24257,13 @@
         <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
@@ -24272,112 +24274,112 @@
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C44" s="2">
         <v>40</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C45" s="2">
         <v>41</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C46" s="2">
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C47" s="2">
         <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C48" s="2">
         <v>44</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="C49" s="2">
         <v>45</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24394,7 +24396,7 @@
         <v>1797</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24411,7 +24413,7 @@
         <v>1797</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24428,7 +24430,7 @@
         <v>1797</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24445,7 +24447,7 @@
         <v>1797</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24462,7 +24464,7 @@
         <v>1797</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24479,7 +24481,7 @@
         <v>1797</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24496,7 +24498,7 @@
         <v>1797</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24513,7 +24515,7 @@
         <v>1797</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24530,7 +24532,7 @@
         <v>1797</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24547,7 +24549,7 @@
         <v>1797</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -24564,7 +24566,7 @@
         <v>1797</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1814</v>
+        <v>1808</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Report (4).xlsx
+++ b/docs/Report (4).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nestech\Downloads\Compressed\Matrix2-main\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6D8E36-078F-470F-AA24-028303C3323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E6D18D-B4AD-4029-A118-2690ED4C4C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5469,10 +5469,10 @@
     <t>hekmat_tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">دانش آموز - فارغ التحصیل </t>
-  </si>
-  <si>
-    <t>عادی حکمت بنیاد</t>
+    <t>student_registration_status</t>
+  </si>
+  <si>
+    <t>student_educational_status</t>
   </si>
 </sst>
 </file>
@@ -23690,7 +23690,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C9" s="2">
         <v>5</v>
@@ -23809,7 +23809,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="C16" s="2">
         <v>12</v>
